--- a/WVS_Dataset/WVS7_Codebook_updated_labels.xlsx
+++ b/WVS_Dataset/WVS7_Codebook_updated_labels.xlsx
@@ -550,7 +550,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -597,7 +597,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -785,7 +785,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -879,7 +879,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1349,7 +1349,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1443,7 +1443,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1913,7 +1913,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2007,7 +2007,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2148,7 +2148,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2242,7 +2242,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2336,7 +2336,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2430,7 +2430,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2519,7 +2519,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -2566,7 +2566,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2655,7 +2655,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -2932,7 +2932,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3026,7 +3026,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -3073,7 +3073,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -3115,7 +3115,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -3298,7 +3298,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -3392,7 +3392,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -3439,7 +3439,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -3820,7 +3820,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -3914,7 +3914,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -4149,7 +4149,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -4290,7 +4290,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -4436,7 +4436,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -4671,7 +4671,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -4723,7 +4723,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -4770,7 +4770,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -4911,7 +4911,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -4958,7 +4958,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -5005,7 +5005,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -5052,7 +5052,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -5099,7 +5099,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -5146,7 +5146,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -5193,7 +5193,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -5240,7 +5240,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -5287,7 +5287,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -5740,7 +5740,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -5980,7 +5980,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -6027,7 +6027,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -6069,7 +6069,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -6111,7 +6111,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -6158,7 +6158,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -6247,7 +6247,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -6435,7 +6435,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -6482,7 +6482,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -6529,7 +6529,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -6618,7 +6618,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -6707,7 +6707,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -6754,7 +6754,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -6848,7 +6848,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -6942,7 +6942,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -6989,7 +6989,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -7036,7 +7036,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -7083,7 +7083,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -7177,7 +7177,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -7271,7 +7271,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -7318,7 +7318,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -7412,7 +7412,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -7543,7 +7543,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -7585,7 +7585,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -7632,7 +7632,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -7679,7 +7679,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -7721,7 +7721,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -7899,7 +7899,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -7951,7 +7951,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -8003,7 +8003,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -8055,7 +8055,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -8107,7 +8107,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -8154,7 +8154,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -8201,7 +8201,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -8567,7 +8567,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -8693,7 +8693,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -8740,7 +8740,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -9775,7 +9775,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -9911,7 +9911,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -9953,7 +9953,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -10000,7 +10000,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -10047,7 +10047,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -10141,7 +10141,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -10188,7 +10188,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -10235,7 +10235,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -10282,7 +10282,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -10329,7 +10329,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -10423,7 +10423,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -10470,7 +10470,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -10611,7 +10611,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -10658,7 +10658,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -10705,7 +10705,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -10752,7 +10752,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -10940,7 +10940,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -10987,7 +10987,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -11222,7 +11222,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -11363,7 +11363,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -11457,7 +11457,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -11504,7 +11504,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -11546,7 +11546,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -11640,7 +11640,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -11687,7 +11687,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -11781,7 +11781,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -11828,7 +11828,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -11932,7 +11932,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -12036,7 +12036,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -12088,7 +12088,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -12140,7 +12140,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -12192,7 +12192,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -12244,7 +12244,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -12343,7 +12343,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -12390,7 +12390,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -12437,7 +12437,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -12479,7 +12479,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -12682,7 +12682,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -12996,7 +12996,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -13248,7 +13248,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -13379,7 +13379,7 @@
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I277" t="inlineStr">
@@ -13421,7 +13421,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -13505,7 +13505,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -13547,7 +13547,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -13631,7 +13631,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -13673,7 +13673,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -13715,7 +13715,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -13757,7 +13757,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -13799,7 +13799,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -13841,7 +13841,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -13883,7 +13883,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -13925,7 +13925,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -13967,7 +13967,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -14182,7 +14182,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -14266,7 +14266,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -14350,7 +14350,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>T</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">

--- a/WVS_Dataset/WVS7_Codebook_updated_labels.xlsx
+++ b/WVS_Dataset/WVS7_Codebook_updated_labels.xlsx
@@ -8248,7 +8248,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -8295,7 +8295,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -8389,7 +8389,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -14056,7 +14056,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>T</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
